--- a/artfynd/A 47992-2025 artfynd.xlsx
+++ b/artfynd/A 47992-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103022428</v>
       </c>
       <c r="B2" t="n">
-        <v>99566</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540510.0790795534</v>
+        <v>540510</v>
       </c>
       <c r="R2" t="n">
-        <v>6504525.273547978</v>
+        <v>6504525</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,19 +751,9 @@
           <t>2022-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
